--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260209_203303.xlsx
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
